--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.21201084605794</v>
+        <v>5.559451762484416</v>
       </c>
       <c r="D2" t="n">
-        <v>34.29848945406645</v>
+        <v>5.573504536285798</v>
       </c>
       <c r="E2" t="n">
-        <v>4.441605363891625</v>
+        <v>0.7217608716323891</v>
       </c>
       <c r="F2" t="n">
-        <v>4.389506722885283</v>
+        <v>0.7132948424688585</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.09522157384119</v>
+        <v>7.002973505749194</v>
       </c>
       <c r="D3" t="n">
-        <v>43.07750289983701</v>
+        <v>7.000094221223515</v>
       </c>
       <c r="E3" t="n">
-        <v>4.441605363891625</v>
+        <v>0.7217608716323891</v>
       </c>
       <c r="F3" t="n">
-        <v>4.389506722885283</v>
+        <v>0.7132948424688585</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
